--- a/output/plots/COMMITTED__baseline__v82_R12_PAK.xlsx
+++ b/output/plots/COMMITTED__baseline__v82_R12_PAK.xlsx
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>391.3185753635506</v>
+        <v>368.9488259631841</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1123.397453445468</v>
+        <v>1004.009956622219</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>118.2856279334299</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1476.607199671986</v>
+        <v>1399.503754947649</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>2234.09231594519</v>
+        <v>1737.312438177103</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>3983.088882952889</v>
+        <v>1702.510781058639</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>6799.865344084459</v>
+        <v>1993.955445318681</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>5261.606180819433</v>
+        <v>2462.823946320007</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>8858.930237471508</v>
+        <v>3002.788896197674</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>6854.871344397801</v>
+        <v>3551.404855717625</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>18784.97610892163</v>
+        <v>4527.762459768239</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>16.925196</v>
       </c>
       <c r="G10">
-        <v>7.748219999999999</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>6.238819529012036</v>
@@ -2467,7 +2467,7 @@
         <v>23.206116</v>
       </c>
       <c r="G11">
-        <v>17.547156</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>7.551885718033875</v>
@@ -2514,7 +2514,7 @@
         <v>17.194128</v>
       </c>
       <c r="G12">
-        <v>26.903712</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>12.45339534044497</v>
@@ -2561,7 +2561,7 @@
         <v>30.86235599999999</v>
       </c>
       <c r="G13">
-        <v>18.868164</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>24.07121771827689</v>
@@ -2608,7 +2608,7 @@
         <v>31.81106400000001</v>
       </c>
       <c r="G14">
-        <v>33.186384</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>14.24097718555269</v>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0.0133300044</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>34.63266</v>
       </c>
       <c r="G15">
-        <v>35.362368</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>22.42804063655473</v>
@@ -2673,13 +2673,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0.368280036</v>
+        <v>0.21024</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0.6157700088</v>
+        <v>0.6217699956</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2687,46 +2687,46 @@
         <v>2020</v>
       </c>
       <c r="B16">
-        <v>0.7113119999999999</v>
+        <v>0.5644600000056</v>
       </c>
       <c r="C16">
-        <v>27.549324</v>
+        <v>25.96635</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>4.183719999999999</v>
       </c>
       <c r="F16">
-        <v>33.548172</v>
+        <v>38.98796</v>
       </c>
       <c r="G16">
-        <v>17.19588</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>36.7316885918895</v>
+        <v>38.03968807358847</v>
       </c>
       <c r="I16">
-        <v>12.7404114081105</v>
+        <v>13.19409192641153</v>
       </c>
       <c r="J16">
-        <v>9.346043999999999</v>
+        <v>9.897889999999999</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>0.51374</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.0263499824</v>
+        <v>0.71832</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
-        <v>2.5037699724</v>
+        <v>2.882479999999997</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2734,16 +2734,16 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>19.35088081150687</v>
+        <v>0.7043039999999999</v>
       </c>
       <c r="C17">
-        <v>66.67379320188714</v>
+        <v>23.20017704916022</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>15.40179589850895</v>
+        <v>5.450690644979091</v>
       </c>
       <c r="F17">
         <v>40.39591824534774</v>
@@ -2752,28 +2752,28 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>55.881462912897</v>
+        <v>32.38721191092174</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>11.23352668839486</v>
       </c>
       <c r="J17">
-        <v>24.33885846</v>
+        <v>23.2705840527738</v>
       </c>
       <c r="K17">
-        <v>11.15984689853505</v>
+        <v>7.360681985984463</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1.311510375759483</v>
+        <v>9.922097378313255</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>4.537424178215978</v>
+        <v>3.956796448937976</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2781,25 +2781,25 @@
         <v>2030</v>
       </c>
       <c r="B18">
-        <v>21.08980796504526</v>
+        <v>0.7707477735849058</v>
       </c>
       <c r="C18">
-        <v>112.867769934269</v>
+        <v>33.6017470931874</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>12.74844179916205</v>
+        <v>16.93654395817142</v>
       </c>
       <c r="F18">
-        <v>75.34052815591039</v>
+        <v>110.9078011364705</v>
       </c>
       <c r="G18">
-        <v>1.499646559375123</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>40.40258902035281</v>
+        <v>41.81924672018982</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2808,19 +2808,19 @@
         <v>23.84593764</v>
       </c>
       <c r="K18">
-        <v>0.2007207770744061</v>
+        <v>0.9454747538517972</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>7.924547193179243</v>
+        <v>26.72933163181936</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>4.537424178215978</v>
+        <v>11.46945988981533</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2828,46 +2828,46 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>31.16985953026339</v>
+        <v>0.8371915471698114</v>
       </c>
       <c r="C19">
-        <v>181.3505855721184</v>
+        <v>30.73445833720342</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>14.53968850771688</v>
+        <v>25.28153469472484</v>
       </c>
       <c r="F19">
-        <v>94.17310139268297</v>
+        <v>123.3387851931275</v>
       </c>
       <c r="G19">
-        <v>25.82802680197826</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>53.85717884411687</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>23.35301682</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K19">
-        <v>0.2007207770744061</v>
+        <v>0.9454747538517972</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>19.77278760482536</v>
+        <v>46.77483201701161</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>4.537424178215978</v>
+        <v>27.15746071979872</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -2875,46 +2875,46 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>35.67238926328699</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>270.7897788720537</v>
+        <v>29.48616</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>8.543163894429332</v>
+        <v>14.41381538145146</v>
       </c>
       <c r="F20">
-        <v>108.9219526624502</v>
+        <v>163.8069352925696</v>
       </c>
       <c r="G20">
-        <v>34.87498178584707</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>38.89125034599204</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>20.757696</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K20">
-        <v>0.2007207770744061</v>
+        <v>0.6711487586474915</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>29.2958717758494</v>
+        <v>77.97769600605537</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>4.537424178215978</v>
+        <v>57.52844810462312</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -2922,46 +2922,46 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>45.03339598402155</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>339.5535371944501</v>
+        <v>29.48616</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>9.878965263449642</v>
+        <v>11.20873439310177</v>
       </c>
       <c r="F21">
-        <v>133.5633466727043</v>
+        <v>206.5233788181706</v>
       </c>
       <c r="G21">
-        <v>51.85971107426096</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>36.16310806961312</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>20.757696</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K21">
-        <v>0.200720777074406</v>
+        <v>0.298439366364213</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>39.03010401288172</v>
+        <v>94.66065043945225</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>4.537424178215991</v>
+        <v>85.7685912639885</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2969,31 +2969,31 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>54.45571979689824</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>404.2014053338742</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>10.142762496</v>
+        <v>7.266995735183695</v>
       </c>
       <c r="F22">
-        <v>145.7211838506097</v>
+        <v>291.3998242514177</v>
       </c>
       <c r="G22">
-        <v>95.50509579569203</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>8.522829331200121</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>20.757696</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -3002,13 +3002,13 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>39.02716184450824</v>
+        <v>107.0648294739877</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>4.537424178215991</v>
+        <v>118.5407635961563</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -3016,22 +3016,22 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>66.18594906449864</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>509.135090933225</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>5.820264181504241</v>
       </c>
       <c r="F23">
-        <v>168.1328179811026</v>
+        <v>354.3708641068549</v>
       </c>
       <c r="G23">
-        <v>121.8962930362994</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>18.655296</v>
+        <v>29.12959875833333</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3049,13 +3049,13 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>46.76695445005583</v>
+        <v>127.3414172788428</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>4.5273064956</v>
+        <v>145.6938840695978</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -3063,31 +3063,31 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>81.38629229462333</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>605.3174125146566</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>4.626479081365479</v>
       </c>
       <c r="F24">
-        <v>191.4553610863093</v>
+        <v>410.228279451992</v>
       </c>
       <c r="G24">
-        <v>135.7432226070343</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>3.061914180539957</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>14.254272</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>54.04260612646633</v>
+        <v>151.1211023313796</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>4.5273064956</v>
+        <v>170.2598317735071</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -3110,22 +3110,22 @@
         <v>2070</v>
       </c>
       <c r="B25">
-        <v>118.9870490075725</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>812.470186435065</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>6.795216291176319</v>
       </c>
       <c r="F25">
-        <v>244.875566189938</v>
+        <v>581.051686588776</v>
       </c>
       <c r="G25">
-        <v>177.534785487705</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3134,22 +3134,22 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>31.23199875833333</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>0.01788100726884077</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>72.0967803688294</v>
+        <v>227.256347944432</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>4.5273064956</v>
+        <v>243.4633807339598</v>
       </c>
     </row>
   </sheetData>
@@ -3916,40 +3916,40 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>3334.346654864629</v>
+        <v>121.3584905660377</v>
       </c>
       <c r="C17">
-        <v>15411.74629276664</v>
+        <v>5786.915647067724</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>2068.465739794379</v>
+        <v>3184.33904348744</v>
       </c>
       <c r="F17">
         <v>11379.16395408093</v>
       </c>
       <c r="G17">
-        <v>1496.358170461454</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>10686.972</v>
+        <v>10032.972</v>
       </c>
       <c r="I17">
-        <v>5160.073</v>
+        <v>3539.74190329035</v>
       </c>
       <c r="J17">
         <v>3262</v>
       </c>
       <c r="K17">
-        <v>21170.04935224698</v>
+        <v>10817.93151184832</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1662.043049999999</v>
+        <v>5527.5</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3963,46 +3963,46 @@
         <v>2030</v>
       </c>
       <c r="B18">
-        <v>3320.706654864629</v>
+        <v>121.3584905660377</v>
       </c>
       <c r="C18">
-        <v>17937.06152468745</v>
+        <v>5300.030444962047</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>2068.465739794379</v>
+        <v>3284.610162064213</v>
       </c>
       <c r="F18">
-        <v>20118.16821701792</v>
+        <v>29615.69097611964</v>
       </c>
       <c r="G18">
-        <v>1496.358170461454</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>10686.972</v>
+        <v>10032.972</v>
       </c>
       <c r="I18">
-        <v>5783.717599816801</v>
+        <v>3532.968513933876</v>
       </c>
       <c r="J18">
         <v>3262</v>
       </c>
       <c r="K18">
-        <v>1043.829510407236</v>
+        <v>1946.291648294892</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>4503.415055319909</v>
+        <v>13797.47434139609</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1848.206499999995</v>
+        <v>4321.10736743698</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -4010,46 +4010,46 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>4518.353197110008</v>
+        <v>121.3584905660377</v>
       </c>
       <c r="C19">
-        <v>25632.41369488564</v>
+        <v>5300.030444962047</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2068.465739794379</v>
+        <v>3395.317579200221</v>
       </c>
       <c r="F19">
-        <v>23902.95506450387</v>
+        <v>31305.76987040681</v>
       </c>
       <c r="G19">
-        <v>3468.711630671269</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>10536.972</v>
+        <v>10032.972</v>
       </c>
       <c r="I19">
-        <v>10066.05980108059</v>
+        <v>13483.35310283089</v>
       </c>
       <c r="J19">
-        <v>3262</v>
+        <v>4362.553272450532</v>
       </c>
       <c r="K19">
-        <v>1043.829510407236</v>
+        <v>1946.291648294892</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>10333.32393366885</v>
+        <v>23660.83266350691</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>1848.206499999995</v>
+        <v>9917.56885073585</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -4057,46 +4057,46 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>4790.812417846761</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>36617.735545535</v>
+        <v>5300.030444962047</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>2068.465739794379</v>
+        <v>3517.547513231941</v>
       </c>
       <c r="F20">
-        <v>26343.24758688622</v>
+        <v>39617.41914629519</v>
       </c>
       <c r="G20">
-        <v>4683.720358024049</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>10032.972</v>
       </c>
       <c r="I20">
-        <v>18403.49521804933</v>
+        <v>14433.57966240587</v>
       </c>
       <c r="J20">
-        <v>2962</v>
+        <v>4456.620827387746</v>
       </c>
       <c r="K20">
-        <v>1043.829510407236</v>
+        <v>1640.093175717788</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>15019.12967520071</v>
+        <v>39014.15496956291</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>1848.206499999995</v>
+        <v>20751.96788927195</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -4104,46 +4104,46 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>6047.998386250544</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>45833.90507580582</v>
+        <v>5220.030444962047</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>2068.465739794379</v>
+        <v>3652.499236972765</v>
       </c>
       <c r="F21">
-        <v>32302.8758108661</v>
+        <v>49948.5766431997</v>
       </c>
       <c r="G21">
-        <v>6964.774519777191</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>7430.571999999999</v>
       </c>
       <c r="I21">
-        <v>27849.67574479375</v>
+        <v>20103.16331151058</v>
       </c>
       <c r="J21">
-        <v>2962</v>
+        <v>4456.620827387746</v>
       </c>
       <c r="K21">
-        <v>1043.829510407236</v>
+        <v>1165.786064589784</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>19808.46961825512</v>
+        <v>47222.97761235387</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>1848.206500000002</v>
+        <v>30826.21987249305</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -4151,46 +4151,46 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>7313.419258245802</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>54284.36816194926</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1362.176</v>
+        <v>975.9596743464538</v>
       </c>
       <c r="F22">
-        <v>35243.30156591249</v>
+        <v>70476.313813612</v>
       </c>
       <c r="G22">
-        <v>12826.36258335912</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>6124.632999999999</v>
       </c>
       <c r="I22">
-        <v>36513.38542056007</v>
+        <v>19181.97631151059</v>
       </c>
       <c r="J22">
-        <v>2962</v>
+        <v>4456.620827387746</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>109.3027414414683</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>19805.77998492179</v>
+        <v>53326.43525413045</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>1848.206500000002</v>
+        <v>42517.20600697071</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -4198,46 +4198,46 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>8888.792514705703</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>68376.99314171703</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>781.6631992350577</v>
       </c>
       <c r="F23">
-        <v>40663.6526732409</v>
+        <v>85706.13345204873</v>
       </c>
       <c r="G23">
-        <v>16370.70817033299</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>50978.71365759688</v>
+        <v>26910.13758882994</v>
       </c>
       <c r="J23">
-        <v>2662</v>
+        <v>4156.620827387747</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>120.7406334582157</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>23612.87564815376</v>
+        <v>63303.4997936002</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>1845.160000000004</v>
+        <v>52203.67877860367</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -4245,46 +4245,46 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>10930.20310161474</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>81294.30734819455</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>863.0193328433244</v>
       </c>
       <c r="F24">
-        <v>46304.3110745853</v>
+        <v>99215.49208942614</v>
       </c>
       <c r="G24">
-        <v>18230.35490290549</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>58156.83856480227</v>
+        <v>29936.6018075125</v>
       </c>
       <c r="J24">
-        <v>2034</v>
+        <v>4456.620827387746</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>132.1764831779169</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>27192.84911513263</v>
+        <v>75004.25806618367</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>1845.160000000004</v>
+        <v>60967.21605882246</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -4292,46 +4292,46 @@
         <v>2070</v>
       </c>
       <c r="B25">
-        <v>15979.99583770783</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>109114.9860911986</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>912.5995556240021</v>
       </c>
       <c r="F25">
-        <v>59224.2198238183</v>
+        <v>140529.8754422974</v>
       </c>
       <c r="G25">
-        <v>23842.97414554191</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>79755.14905252394</v>
+        <v>46698.96096471493</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>4456.620827387747</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>157.1246160999423</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>36076.37840302187</v>
+        <v>112466.4911855017</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1845.160000000004</v>
+        <v>87081.4957964269</v>
       </c>
     </row>
   </sheetData>
@@ -4784,7 +4784,7 @@
         <v>2.407982919342419</v>
       </c>
       <c r="G10">
-        <v>272.1538461538461</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>90.80000000000001</v>
@@ -4831,7 +4831,7 @@
         <v>408.0830201823209</v>
       </c>
       <c r="G11">
-        <v>344.1846153846153</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>225.16</v>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>1.852</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>51.218</v>
+        <v>60</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>117.88</v>
+        <v>140</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5098,16 +5098,16 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>552.2683309729258</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>2077.349258553329</v>
+        <v>152.3831294135448</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>18.16372828621858</v>
       </c>
       <c r="F17">
         <v>275.848270095947</v>
@@ -5125,19 +5125,19 @@
         <v>406.8</v>
       </c>
       <c r="K17">
-        <v>4187.209870824907</v>
+        <v>2163.586302369664</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>161.4586099999998</v>
+        <v>905.7409638554218</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>122.4692999999996</v>
+        <v>122.4692999999983</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -5148,16 +5148,16 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>839.8950002499902</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20.05422371535477</v>
       </c>
       <c r="F18">
-        <v>1790.701024389341</v>
+        <v>3690.205576209686</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>195.7361199633602</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>650.7869643973154</v>
+        <v>1653.994868279218</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>494.580173487397</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -5192,31 +5192,31 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>242.409308449076</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1539.070434039636</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>22.14148342720138</v>
       </c>
       <c r="F19">
-        <v>848.9878005360108</v>
+        <v>430.0462098962555</v>
       </c>
       <c r="G19">
-        <v>693.7423261342537</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>911.7684402527573</v>
+        <v>1997.076917779404</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>220.1106544901064</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -5225,13 +5225,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1165.981775669788</v>
+        <v>1972.671664422163</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1119.292296659774</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -5239,31 +5239,31 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>63.69984414735035</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>2197.064370129874</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>24.44598680634399</v>
       </c>
       <c r="F20">
-        <v>585.3365356462</v>
+        <v>1759.607886347403</v>
       </c>
       <c r="G20">
-        <v>243.0017454705562</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>1826.487083393748</v>
+        <v>190.0453119149944</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>78.81351098744305</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>939.0131483063719</v>
+        <v>3070.664461211204</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>1.2</v>
+        <v>2168.07980770722</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -5286,28 +5286,28 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>269.3571936807568</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>1859.233906054165</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>26.99034474816488</v>
       </c>
       <c r="F21">
-        <v>1512.329634439947</v>
+        <v>2386.635489024872</v>
       </c>
       <c r="G21">
-        <v>456.2108323506284</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2305.974105348884</v>
+        <v>1503.541032607719</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -5319,13 +5319,13 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1009.085988610882</v>
+        <v>1701.76452855819</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>60.47200000000002</v>
+        <v>2075.322396644219</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -5333,46 +5333,46 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>268.9891743990515</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>2679.092617228688</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>29.79952150819878</v>
       </c>
       <c r="F22">
-        <v>590.4931339286203</v>
+        <v>4107.955417001803</v>
       </c>
       <c r="G22">
-        <v>1172.317612716387</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>1916.979335153263</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>21.86054828829366</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>117.3420733333344</v>
+        <v>1360.450564499895</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>185.5000000000007</v>
+        <v>2523.697226895534</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -5380,46 +5380,46 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>933.3029822649058</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>4561.042300641056</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>32.90107964174778</v>
       </c>
       <c r="F23">
-        <v>1492.153241648003</v>
+        <v>3454.046947869668</v>
       </c>
       <c r="G23">
-        <v>708.869117394772</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>3038.797647407365</v>
+        <v>1691.364255463872</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2.28757840334948</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>840.3651793130596</v>
+        <v>2901.15387174937</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>121.8600000000001</v>
+        <v>2059.76385432659</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -5427,46 +5427,46 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>408.2821173818076</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>3423.357841545492</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>36.32545043700807</v>
       </c>
       <c r="F24">
-        <v>1148.090113848833</v>
+        <v>2721.830161055437</v>
       </c>
       <c r="G24">
-        <v>371.9293465145018</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>1631.361101404438</v>
+        <v>605.2928437365113</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>185.6</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2.287169943940246</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>1366.78165779309</v>
+        <v>3994.146522795911</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2247.287629531154</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -5474,46 +5474,46 @@
         <v>2070</v>
       </c>
       <c r="B25">
-        <v>642.1088888706847</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>4100.869183852694</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>22.14026069325447</v>
       </c>
       <c r="F25">
-        <v>1460.266005115379</v>
+        <v>4299.713465479205</v>
       </c>
       <c r="G25">
-        <v>968.8835236984074</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>3072.337039746982</v>
+        <v>2722.285702588693</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>203.4</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2.494813292202542</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1706.097103700411</v>
+        <v>5500.225259445685</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0.3</v>
+        <v>3713.094074017136</v>
       </c>
     </row>
   </sheetData>
@@ -5763,7 +5763,7 @@
         <v>2025</v>
       </c>
       <c r="B9">
-        <v>132.33075</v>
+        <v>85.8621717035758</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5778,13 +5778,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>47.7548990917792</v>
+        <v>31.74108951807052</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>1.639199006744389</v>
+        <v>1.729971180093749</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5792,7 +5792,7 @@
         <v>2030</v>
       </c>
       <c r="B10">
-        <v>170.6813</v>
+        <v>153.5674831047381</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -5801,13 +5801,13 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1.0176301059375</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>58.91886153846152</v>
+        <v>48.93877267990072</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2035</v>
       </c>
       <c r="B11">
-        <v>219.6552763888889</v>
+        <v>193.3812750207813</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -5830,13 +5830,13 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2.759722164932219</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>83.89498888461536</v>
+        <v>63.88556240894296</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>2040</v>
       </c>
       <c r="B12">
-        <v>270.319</v>
+        <v>227.4898885379145</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -5859,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>5.742028529794086</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>125.39064</v>
+        <v>79.42776652505187</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>2045</v>
       </c>
       <c r="B13">
-        <v>330.5544633333333</v>
+        <v>265.4742621908193</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -5888,13 +5888,13 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>10.84747126915656</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2.340549243656249</v>
       </c>
       <c r="G13">
-        <v>169.7974375884147</v>
+        <v>95.90055465792776</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2050</v>
       </c>
       <c r="B14">
-        <v>392.2538200000001</v>
+        <v>298.2472210640068</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -5917,19 +5917,19 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>19.58753428616193</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6.073841416042312</v>
       </c>
       <c r="G14">
-        <v>226.2939285365853</v>
+        <v>114.6715375145281</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>31.90494887188555</v>
+        <v>31.90494887188556</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -5937,7 +5937,7 @@
         <v>2055</v>
       </c>
       <c r="B15">
-        <v>463.6447009090909</v>
+        <v>347.1051291951938</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -5946,19 +5946,19 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>29.65408413526216</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>11.79904790418974</v>
       </c>
       <c r="G15">
-        <v>290.8099246326772</v>
+        <v>128.6715716111984</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>44.98049326260502</v>
+        <v>44.98049326260501</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -5966,7 +5966,7 @@
         <v>2060</v>
       </c>
       <c r="B16">
-        <v>527.7992909090908</v>
+        <v>390.047415990327</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5975,19 +5975,19 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>43.58990293128799</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>15.03372850792441</v>
       </c>
       <c r="G16">
-        <v>366.0534339759037</v>
+        <v>145.1895044637431</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>54.26317207055483</v>
+        <v>69.26756467298638</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -5995,7 +5995,7 @@
         <v>2070</v>
       </c>
       <c r="B17">
-        <v>679.7687000000001</v>
+        <v>512.3508236353561</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -6004,19 +6004,19 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>80.4050209099059</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>42.92343314757503</v>
       </c>
       <c r="G17">
-        <v>476.8746378571427</v>
+        <v>177.1542625032086</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>130.7991687290964</v>
+        <v>161.7236954538186</v>
       </c>
     </row>
   </sheetData>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>325.0970951900258</v>
+        <v>308.6349521673981</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>368.3092047920779</v>
+        <v>387.5648435963337</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>570.5207882535507</v>
+        <v>548.1510388531841</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -6437,31 +6437,31 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D9">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E9">
-        <v>924.3775437866514</v>
+        <v>484.6545508290774</v>
       </c>
       <c r="F9">
-        <v>0.2167822872195472</v>
+        <v>57.97591236721932</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-1.51032</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>10.78550869203841</v>
+        <v>3.5892872176461</v>
       </c>
       <c r="J9">
         <v>31.58572751528569</v>
       </c>
       <c r="K9">
-        <v>1558.442070593878</v>
+        <v>1826.736854506157</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -6470,13 +6470,13 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>-0.1467526648486058</v>
       </c>
       <c r="O9">
-        <v>147.3527203123218</v>
+        <v>31.58572751528569</v>
       </c>
       <c r="P9">
-        <v>1241.683081378898</v>
+        <v>1004.009956622219</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -6487,16 +6487,16 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D10">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E10">
-        <v>1317.807517910998</v>
+        <v>562.5896587460787</v>
       </c>
       <c r="F10">
-        <v>0.2339878717009769</v>
+        <v>971.7769518326789</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -6505,13 +6505,13 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.7225947974678619</v>
+        <v>3.40370911386647</v>
       </c>
       <c r="J10">
-        <v>29.62638669618233</v>
+        <v>29.95264020202494</v>
       </c>
       <c r="K10">
-        <v>1063.211879323572</v>
+        <v>1714.723091789007</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -6523,10 +6523,10 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>25.2877878765401</v>
       </c>
       <c r="P10">
-        <v>1476.607199671986</v>
+        <v>1399.503754947649</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -6537,16 +6537,16 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D11">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E11">
-        <v>2067.700294981462</v>
+        <v>489.0841741952254</v>
       </c>
       <c r="F11">
-        <v>0.2528394476741414</v>
+        <v>3090.932639339783</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -6555,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.7225947974678619</v>
+        <v>3.40370911386647</v>
       </c>
       <c r="J11">
-        <v>29.62638669618233</v>
+        <v>29.95264020202494</v>
       </c>
       <c r="K11">
-        <v>688.6675776645933</v>
+        <v>2201.898386415952</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -6570,13 +6570,13 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>-90.12396869280001</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>25.2877878765401</v>
       </c>
       <c r="P11">
-        <v>2234.09231594519</v>
+        <v>1737.312438177103</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D12">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E12">
-        <v>3122.592148728379</v>
+        <v>598.9979507133755</v>
       </c>
       <c r="F12">
-        <v>0.272459388799013</v>
+        <v>3732.505898673088</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -6605,13 +6605,13 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.7225947974678619</v>
+        <v>2.41613553113097</v>
       </c>
       <c r="J12">
-        <v>29.62638669618233</v>
+        <v>21.26199267395254</v>
       </c>
       <c r="K12">
-        <v>684.749447459492</v>
+        <v>2244.620794459548</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -6623,10 +6623,10 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>25.2877878765401</v>
       </c>
       <c r="P12">
-        <v>3983.088882952889</v>
+        <v>1702.510781058639</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -6637,16 +6637,16 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D13">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E13">
-        <v>4019.978864729306</v>
+        <v>636.919316353015</v>
       </c>
       <c r="F13">
-        <v>0.2922571522073331</v>
+        <v>4527.270970530034</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -6655,13 +6655,13 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.7225947974678618</v>
+        <v>1.074381718911167</v>
       </c>
       <c r="J13">
-        <v>29.62638669618233</v>
+        <v>9.454559126418273</v>
       </c>
       <c r="K13">
-        <v>636.0973423981239</v>
+        <v>2291.073629075113</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -6673,10 +6673,10 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>23.6332472731948</v>
       </c>
       <c r="P13">
-        <v>6799.865344084459</v>
+        <v>1993.955445318681</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -6687,16 +6687,16 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D14">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E14">
-        <v>4866.812153090755</v>
+        <v>394.3578017114377</v>
       </c>
       <c r="F14">
-        <v>0.3120053370917559</v>
+        <v>5338.756754962789</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>636.4270973708549</v>
+        <v>2046.583797192817</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -6723,10 +6723,10 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.102274128688329</v>
       </c>
       <c r="P14">
-        <v>5261.606180819433</v>
+        <v>2462.823946320007</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -6737,16 +6737,16 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D15">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E15">
-        <v>6091.344939196301</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="F15">
-        <v>0.3310137100070674</v>
+        <v>6231.465976546207</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -6761,10 +6761,10 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>495.9126465230621</v>
+        <v>2105.837129389162</v>
       </c>
       <c r="L15">
-        <v>-138.6762539057669</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.42690895506446</v>
       </c>
       <c r="P15">
-        <v>8858.930237471508</v>
+        <v>3002.788896197674</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -6787,16 +6787,16 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D16">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E16">
-        <v>7178.173541762352</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="F16">
-        <v>0.3491591812460964</v>
+        <v>7281.53986740123</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>366.833688933229</v>
+        <v>2108.558906623331</v>
       </c>
       <c r="L16">
-        <v>-185.9078245805198</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -6823,10 +6823,10 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.751485816148909</v>
       </c>
       <c r="P16">
-        <v>6854.871344397801</v>
+        <v>3551.404855717625</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -6837,16 +6837,16 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="D17">
-        <v>1576.8</v>
+        <v>653.079024</v>
       </c>
       <c r="E17">
-        <v>10369.91479248211</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0.3810765264380302</v>
+        <v>9738.120422446435</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -6855,16 +6855,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.06437162616782677</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.7080878878460944</v>
       </c>
       <c r="K17">
-        <v>107.7127221817021</v>
+        <v>1826.446110795794</v>
       </c>
       <c r="L17">
-        <v>-251.678837933345</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -6873,10 +6873,10 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.751485816148909</v>
       </c>
       <c r="P17">
-        <v>18784.97610892163</v>
+        <v>4527.762459768239</v>
       </c>
     </row>
   </sheetData>
@@ -7274,7 +7274,7 @@
         <v>2025</v>
       </c>
       <c r="B11">
-        <v>500.5789570765567</v>
+        <v>343.389019236223</v>
       </c>
       <c r="C11">
         <v>260.3229418542278</v>
@@ -7283,22 +7283,22 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>658.0946912061676</v>
+        <v>433.4848746977469</v>
       </c>
       <c r="F11">
         <v>31.26987024013285</v>
       </c>
       <c r="G11">
-        <v>800.8349533421701</v>
+        <v>1380.980024405412</v>
       </c>
       <c r="H11">
-        <v>44.58167590669871</v>
+        <v>63.24543676407224</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>984.2794915442622</v>
+        <v>802.5367634282601</v>
       </c>
       <c r="K11">
         <v>31.26987024013284</v>
@@ -7312,34 +7312,34 @@
         <v>2030</v>
       </c>
       <c r="B12">
-        <v>724.7608287545855</v>
+        <v>501.9386360590778</v>
       </c>
       <c r="C12">
-        <v>365.6198484027769</v>
+        <v>280.8454777927381</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>843.6844147314753</v>
+        <v>749.8098223990888</v>
       </c>
       <c r="F12">
-        <v>29.33012282922051</v>
+        <v>29.6531138000047</v>
       </c>
       <c r="G12">
-        <v>767.62527186964</v>
+        <v>1347.771040580733</v>
       </c>
       <c r="H12">
-        <v>53.52692770346338</v>
+        <v>69.59970305355667</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1171.300785105146</v>
+        <v>1017.709161252713</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>25.0349099977747</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -7350,34 +7350,34 @@
         <v>2035</v>
       </c>
       <c r="B13">
-        <v>1072.250605449998</v>
+        <v>503.4911521799684</v>
       </c>
       <c r="C13">
-        <v>538.7145309894438</v>
+        <v>246.87738247953</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1129.873577418592</v>
+        <v>973.1882369747402</v>
       </c>
       <c r="F13">
-        <v>29.33012282922051</v>
+        <v>29.6531138000047</v>
       </c>
       <c r="G13">
-        <v>665.2521671176019</v>
+        <v>1743.88731919192</v>
       </c>
       <c r="H13">
-        <v>67.27415242290466</v>
+        <v>87.33435326263809</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1427.405678221858</v>
+        <v>1162.540533432084</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>25.0349099977747</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -7388,34 +7388,34 @@
         <v>2040</v>
       </c>
       <c r="B14">
-        <v>1076.47184909377</v>
+        <v>535.6387638046257</v>
       </c>
       <c r="C14">
-        <v>814.2481356830333</v>
+        <v>373.1465124155032</v>
       </c>
       <c r="D14">
-        <v>5.927775490005777</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1497.640043832051</v>
+        <v>1198.660200765988</v>
       </c>
       <c r="F14">
-        <v>29.33012282922051</v>
+        <v>21.04937274721302</v>
       </c>
       <c r="G14">
-        <v>660.7832167984094</v>
+        <v>1881.480595681785</v>
       </c>
       <c r="H14">
-        <v>87.21206765461669</v>
+        <v>101.6228374905461</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>1747.451441853656</v>
+        <v>1325.558690542141</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>25.0349099977747</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -7426,34 +7426,34 @@
         <v>2045</v>
       </c>
       <c r="B15">
-        <v>964.1397684449554</v>
+        <v>571.4314296145321</v>
       </c>
       <c r="C15">
-        <v>1123.296060868614</v>
+        <v>411.0678780551427</v>
       </c>
       <c r="D15">
-        <v>5.992207832288448</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1913.279558169875</v>
+        <v>1460.438929353197</v>
       </c>
       <c r="F15">
-        <v>29.33012282922051</v>
+        <v>9.360013535154092</v>
       </c>
       <c r="G15">
-        <v>613.515721865504</v>
+        <v>1946.457219775181</v>
       </c>
       <c r="H15">
-        <v>100.9508097947325</v>
+        <v>113.2673140321414</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2258.392104748981</v>
+        <v>1629.21916247194</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>23.39691480046285</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -7464,34 +7464,34 @@
         <v>2050</v>
       </c>
       <c r="B16">
-        <v>604.121851051019</v>
+        <v>601.8766535582661</v>
       </c>
       <c r="C16">
-        <v>1402.228678800404</v>
+        <v>394.3578017114377</v>
       </c>
       <c r="D16">
-        <v>6.056640174571118</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2341.629710670495</v>
+        <v>1693.746299349449</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>613.515721865504</v>
+        <v>1915.108674154421</v>
       </c>
       <c r="H16">
-        <v>115.213348346756</v>
+        <v>124.2333531010887</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>3045.268711461003</v>
+        <v>2112.05984536882</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3.071251387401446</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -7502,34 +7502,34 @@
         <v>2055</v>
       </c>
       <c r="B17">
-        <v>308.4306827516735</v>
+        <v>611.445966219159</v>
       </c>
       <c r="C17">
-        <v>1727.329874054372</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="D17">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2877.966427695744</v>
+        <v>2023.957173990417</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>477.5633636353054</v>
+        <v>2022.422532852332</v>
       </c>
       <c r="H17">
-        <v>131.2648641702303</v>
+        <v>134.360033267199</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>4039.197339743561</v>
+        <v>2629.363294653401</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>3.392639865513817</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -7540,34 +7540,34 @@
         <v>2060</v>
       </c>
       <c r="B18">
-        <v>88.22763048620732</v>
+        <v>621.0152788800519</v>
       </c>
       <c r="C18">
-        <v>1989.73857735101</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="D18">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>3413.217229039979</v>
+        <v>2387.261219638568</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>326.3839557786512</v>
+        <v>2022.422865358931</v>
       </c>
       <c r="H18">
-        <v>148.6220692464002</v>
+        <v>143.9012429251762</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>5177.327126828234</v>
+        <v>3152.852904599919</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>3.71397095798742</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -7578,34 +7578,34 @@
         <v>2070</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>634.6942691354343</v>
       </c>
       <c r="C19">
-        <v>2384.504166209496</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>4634.793023710462</v>
+        <v>3508.406048339512</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.7010070089676336</v>
       </c>
       <c r="G19">
-        <v>103.6196387387974</v>
+        <v>1751.030957439221</v>
       </c>
       <c r="H19">
-        <v>192.5386686874936</v>
+        <v>163.5788582586954</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>6852.186468109068</v>
+        <v>4034.236300889891</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>3.71397095798742</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -7861,13 +7861,13 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>5.9011164242798</v>
+        <v>6.227896248337498</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>32.16572276248839</v>
+        <v>104.387768328948</v>
       </c>
       <c r="F9">
         <v>0.01079736435703125</v>
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>861.2393210003153</v>
+        <v>776.7068685731133</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7896,16 +7896,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.001025251128</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>8.406444898344598E-05</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>973.8786031698305</v>
+        <v>973.8795443565097</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>37.09262243397674</v>
+        <v>37.09262243397673</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7928,13 +7928,13 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.0001206853882491145</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1082.53948789807</v>
+        <v>1082.539367212682</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -7948,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>73.08533983205068</v>
+        <v>73.08533983205066</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7957,13 +7957,13 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.0001732594826108674</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1182.099751703848</v>
+        <v>1182.099578444366</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.0003000949609423365</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1371.705634645255</v>
+        <v>1371.705334550294</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -8015,13 +8015,13 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.0005137358312727469</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1685.275881783636</v>
+        <v>1685.275368047805</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -8035,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>161.9297757453781</v>
+        <v>161.929775745378</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -8044,13 +8044,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.0008898187383297877</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1987.118727163866</v>
+        <v>1987.117837345128</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -8064,7 +8064,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>195.3474194539974</v>
+        <v>249.363232822751</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -8073,13 +8073,13 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.001523290387091034</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>2376.626183238008</v>
+        <v>2214.57721984136</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>470.877007424747</v>
+        <v>582.2053036337468</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -8102,13 +8102,13 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.0040975387056</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>2684.907683325759</v>
+        <v>2350.918697160053</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -8418,22 +8418,22 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>171.9176367304051</v>
+        <v>114.2679222650539</v>
       </c>
       <c r="F9">
         <v>16.99164216607035</v>
       </c>
       <c r="G9">
-        <v>249.1595458293232</v>
+        <v>512.612105993562</v>
       </c>
       <c r="H9">
-        <v>37.21365846392253</v>
+        <v>51.5666404507305</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>50.41467874875816</v>
+        <v>6.537094828015459</v>
       </c>
       <c r="K9">
         <v>16.99164216607036</v>
@@ -8444,34 +8444,34 @@
         <v>2030</v>
       </c>
       <c r="B10">
-        <v>348.7795305970911</v>
+        <v>370.5887802986966</v>
       </c>
       <c r="C10">
-        <v>365.6198484027769</v>
+        <v>280.8454777927381</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>212.1079015384615</v>
+        <v>176.1795816476426</v>
       </c>
       <c r="F10">
-        <v>20.14832181805451</v>
+        <v>14.0969532961</v>
       </c>
       <c r="G10">
-        <v>211.333507359275</v>
+        <v>583.6305991301112</v>
       </c>
       <c r="H10">
-        <v>44.44257353142856</v>
+        <v>58.99221172216225</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>74.95299566022426</v>
+        <v>11.42243414301294</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>22.81175625373695</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -8479,34 +8479,34 @@
         <v>2035</v>
       </c>
       <c r="B11">
-        <v>486.8192959626826</v>
+        <v>444.2876239321487</v>
       </c>
       <c r="C11">
-        <v>538.7145309894438</v>
+        <v>246.87738247953</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>302.0219599846153</v>
+        <v>229.9880246721947</v>
       </c>
       <c r="F11">
-        <v>0.07463530872845739</v>
+        <v>15.17379733780058</v>
       </c>
       <c r="G11">
-        <v>148.7029033104683</v>
+        <v>769.3987086758484</v>
       </c>
       <c r="H11">
-        <v>55.55469472068226</v>
+        <v>74.53089758263269</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>126.5853782148663</v>
+        <v>22.3499957164643</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>25.03490999777471</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -8514,34 +8514,34 @@
         <v>2040</v>
       </c>
       <c r="B12">
-        <v>462.7115219783352</v>
+        <v>533.3313798875151</v>
       </c>
       <c r="C12">
-        <v>814.2481356830333</v>
+        <v>373.1465124155031</v>
       </c>
       <c r="D12">
-        <v>5.927775490005776</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>451.406304</v>
+        <v>285.9399594901868</v>
       </c>
       <c r="F12">
-        <v>24.49344964888332</v>
+        <v>21.04937274721301</v>
       </c>
       <c r="G12">
-        <v>145.6262915178378</v>
+        <v>769.1333281785029</v>
       </c>
       <c r="H12">
-        <v>71.5641082173134</v>
+        <v>86.62337264689199</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>191.4116262753805</v>
+        <v>45.61991275741877</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>21.3197945582208</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -8549,34 +8549,34 @@
         <v>2045</v>
       </c>
       <c r="B13">
-        <v>369.7526106486316</v>
+        <v>571.4314296145321</v>
       </c>
       <c r="C13">
-        <v>1123.296060868614</v>
+        <v>411.0678780551426</v>
       </c>
       <c r="D13">
-        <v>5.992207832288447</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>611.2707753182927</v>
+        <v>353.6679740457025</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9.360013535154092</v>
       </c>
       <c r="G13">
-        <v>78.9363422081274</v>
+        <v>754.1502113958049</v>
       </c>
       <c r="H13">
-        <v>81.92114555936934</v>
+        <v>95.88374032934504</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>263.333807028218</v>
+        <v>85.90583560630496</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>23.39691480046286</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8584,34 +8584,34 @@
         <v>2050</v>
       </c>
       <c r="B14">
-        <v>214.1171562081283</v>
+        <v>601.8766535582661</v>
       </c>
       <c r="C14">
-        <v>1402.228678800404</v>
+        <v>394.3578017114376</v>
       </c>
       <c r="D14">
-        <v>6.056640174571118</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>814.6581427317071</v>
+        <v>434.6833641500535</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>16.48900091384368</v>
+        <v>692.8938111410209</v>
       </c>
       <c r="H14">
-        <v>92.53305556732394</v>
+        <v>104.465820319822</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>358.4050963268667</v>
+        <v>135.8378393705036</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>3.071251387401446</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -8619,34 +8619,34 @@
         <v>2055</v>
       </c>
       <c r="B15">
-        <v>88.34033292553653</v>
+        <v>611.445966219159</v>
       </c>
       <c r="C15">
-        <v>1727.329874054372</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="D15">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1046.915728677638</v>
+        <v>505.6942302553973</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>752.0312623763732</v>
       </c>
       <c r="H15">
-        <v>104.4805466896226</v>
+        <v>112.32029818263</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>472.8153844049304</v>
+        <v>179.8628145719208</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3.392639865513817</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8654,34 +8654,34 @@
         <v>2060</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>566.6738312229893</v>
       </c>
       <c r="C16">
-        <v>1989.73857735101</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="D16">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1317.792362313253</v>
+        <v>576.8036386980031</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>900.9263335934656</v>
       </c>
       <c r="H16">
-        <v>117.2687099904001</v>
+        <v>119.5899094762314</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>618.3457520486002</v>
+        <v>201.4672953808551</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3.713970957987421</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -8689,34 +8689,34 @@
         <v>2070</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>634.6942691354342</v>
       </c>
       <c r="C17">
-        <v>2384.504166209496</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>6.12107251685379</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1716.748696285714</v>
+        <v>792.279704342821</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.7010070089676337</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1022.593480228744</v>
       </c>
       <c r="H17">
-        <v>150.2334242794936</v>
+        <v>134.9643138462991</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>934.4618767113503</v>
+        <v>242.4047505316079</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>3.71397095798742</v>
       </c>
     </row>
   </sheetData>
@@ -9134,10 +9134,10 @@
         <v>2025</v>
       </c>
       <c r="B9">
-        <v>257.6413837374894</v>
+        <v>100.4514458971557</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>71.20401619028696</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -9149,13 +9149,13 @@
         <v>3.885238051482514</v>
       </c>
       <c r="G9">
-        <v>476.3907</v>
+        <v>309.1038181328729</v>
       </c>
       <c r="H9">
         <v>10.24841285454998</v>
       </c>
       <c r="I9">
-        <v>358.9180143515692</v>
+        <v>473.7092053906528</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -9167,10 +9167,10 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0.0005776848191554413</v>
+        <v>0.02315273313414202</v>
       </c>
       <c r="N9">
-        <v>49.80526222660325</v>
+        <v>14.54264797288968</v>
       </c>
       <c r="O9">
         <v>10.24841285454998</v>
@@ -9184,10 +9184,10 @@
         <v>2030</v>
       </c>
       <c r="B10">
-        <v>375.9812981574944</v>
+        <v>131.3498557603812</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>73.8172323805739</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -9199,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>614.4526799999999</v>
+        <v>552.8429391770572</v>
       </c>
       <c r="H10">
-        <v>9.181801011166005</v>
+        <v>15.55616050390468</v>
       </c>
       <c r="I10">
-        <v>359.8635740062311</v>
+        <v>496.399481215471</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -9214,16 +9214,16 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>3.663468381375</v>
       </c>
       <c r="M10">
-        <v>0.0008004184348377879</v>
+        <v>0.0005391177975954416</v>
       </c>
       <c r="N10">
-        <v>82.47845248169715</v>
+        <v>24.08289899835864</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.223153744037754</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -9234,10 +9234,10 @@
         <v>2035</v>
       </c>
       <c r="B11">
-        <v>585.4313094873154</v>
+        <v>59.20352824781965</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>71.46739097666443</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -9249,13 +9249,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>790.7589950000001</v>
+        <v>696.1725900748129</v>
       </c>
       <c r="H11">
-        <v>29.25548752049205</v>
+        <v>14.47931646220398</v>
       </c>
       <c r="I11">
-        <v>284.1371868232393</v>
+        <v>656.3846420760549</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -9264,13 +9264,13 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>9.934999793755992</v>
       </c>
       <c r="M11">
-        <v>0.0011972926224</v>
+        <v>0.000806430403862914</v>
       </c>
       <c r="N11">
-        <v>145.7014087024158</v>
+        <v>42.54338198788974</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -9284,10 +9284,10 @@
         <v>2040</v>
       </c>
       <c r="B12">
-        <v>613.7603271154347</v>
+        <v>2.307383917110581</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>69.11754957275497</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -9299,13 +9299,13 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>973.1484</v>
+        <v>818.963598736492</v>
       </c>
       <c r="H12">
-        <v>4.836673180337188</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>243.2784909826977</v>
+        <v>750.1642606168867</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -9314,16 +9314,16 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>20.67130270725871</v>
       </c>
       <c r="M12">
-        <v>0.001325733303272727</v>
+        <v>0.001102604892668789</v>
       </c>
       <c r="N12">
-        <v>238.5831398763013</v>
+        <v>69.66393630660428</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.715115439553784</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -9334,10 +9334,10 @@
         <v>2045</v>
       </c>
       <c r="B13">
-        <v>594.3871577963237</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>60.15996000724446</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -9349,13 +9349,13 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1189.996068</v>
+        <v>955.7073438869495</v>
       </c>
       <c r="H13">
-        <v>29.33012282922051</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>241.4538776453556</v>
+        <v>788.5261910341208</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -9364,13 +9364,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>39.0508965689636</v>
       </c>
       <c r="M13">
-        <v>0.001668078562909091</v>
+        <v>0.001648304025736972</v>
       </c>
       <c r="N13">
-        <v>421.2359948443286</v>
+        <v>122.9967781046848</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -9384,10 +9384,10 @@
         <v>2050</v>
       </c>
       <c r="B14">
-        <v>390.0046948428908</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>51.20237044173398</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -9399,13 +9399,13 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1412.113752</v>
+        <v>1073.689995830425</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>296.9422617580922</v>
+        <v>791.0071367405073</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -9414,13 +9414,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>70.51512343018294</v>
       </c>
       <c r="M14">
-        <v>0.001979393832</v>
+        <v>0.001957417094776673</v>
       </c>
       <c r="N14">
-        <v>711.4231171296681</v>
+        <v>207.7285710317285</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>2055</v>
       </c>
       <c r="B15">
-        <v>220.090349826137</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>41.63305778084104</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -9449,13 +9449,13 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1669.120923272728</v>
+        <v>1249.578465102698</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>197.0747568289391</v>
+        <v>816.3172139459172</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -9464,13 +9464,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>106.7547028869438</v>
       </c>
       <c r="M15">
-        <v>0.002255951007692309</v>
+        <v>0.002353995798186814</v>
       </c>
       <c r="N15">
-        <v>1162.694395710732</v>
+        <v>342.912345400413</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -9484,10 +9484,10 @@
         <v>2060</v>
       </c>
       <c r="B16">
-        <v>88.22763048620732</v>
+        <v>54.3414476570625</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>32.06374511994809</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -9499,13 +9499,13 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1900.077447272727</v>
+        <v>1404.170697565177</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>108.3876592891965</v>
+        <v>660.3701149883145</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -9514,13 +9514,13 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>156.9236505526368</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>0.002712825383612198</v>
       </c>
       <c r="N16">
-        <v>1584.316759287081</v>
+        <v>565.2933269157564</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>16.77546421037011</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -9549,13 +9549,13 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>2447.16732</v>
+        <v>1844.462965087282</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>337.3802475937196</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -9564,13 +9564,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>289.4580752756613</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>0.003445929467451136</v>
       </c>
       <c r="N17">
-        <v>2235.356807218757</v>
+        <v>1087.414896077503</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -9784,13 +9784,13 @@
         <v>4.029815219512499</v>
       </c>
       <c r="D9">
-        <v>160.5916703987895</v>
+        <v>290.2709446922496</v>
       </c>
       <c r="E9">
-        <v>7.3566423936</v>
+        <v>11.64484621585057</v>
       </c>
       <c r="F9">
-        <v>22.82022956858555</v>
+        <v>4.750152054241501</v>
       </c>
       <c r="G9">
         <v>4.029815219512499</v>
@@ -9807,13 +9807,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>196.4271652530058</v>
+        <v>267.7409602351505</v>
       </c>
       <c r="E10">
-        <v>9.083553753599999</v>
+        <v>10.60686814914783</v>
       </c>
       <c r="F10">
-        <v>39.99073379339416</v>
+        <v>8.324283754832118</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -9830,13 +9830,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>232.4120769838943</v>
+        <v>318.1039684400169</v>
       </c>
       <c r="E11">
-        <v>11.7182604096</v>
+        <v>12.80252856421329</v>
       </c>
       <c r="F11">
-        <v>72.57940340650572</v>
+        <v>15.10778851504801</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -9853,13 +9853,13 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>271.8784342978738</v>
+        <v>362.1830068863948</v>
       </c>
       <c r="E12">
-        <v>15.646633704</v>
+        <v>14.99818897927875</v>
       </c>
       <c r="F12">
-        <v>135.3569239981262</v>
+        <v>28.17526303375231</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -9876,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>293.1255020120211</v>
+        <v>403.7808173452552</v>
       </c>
       <c r="E13">
-        <v>19.0279961568</v>
+        <v>17.38162530380968</v>
       </c>
       <c r="F13">
-        <v>202.116668231179</v>
+        <v>48.61121421065625</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -9899,13 +9899,13 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>300.0844591935681</v>
+        <v>431.2077262728925</v>
       </c>
       <c r="E14">
-        <v>22.67831338560002</v>
+        <v>19.76506162834061</v>
       </c>
       <c r="F14">
-        <v>290.1646162208319</v>
+        <v>83.21806691878342</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -9922,13 +9922,13 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>280.4886068063663</v>
+        <v>454.0740565300418</v>
       </c>
       <c r="E15">
-        <v>26.78206152960003</v>
+        <v>22.03649127003249</v>
       </c>
       <c r="F15">
-        <v>416.5688324640337</v>
+        <v>119.470297335939</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -9945,13 +9945,13 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>217.9962964894547</v>
+        <v>461.1264167771508</v>
       </c>
       <c r="E16">
-        <v>31.35335925600009</v>
+        <v>24.30709733317408</v>
       </c>
       <c r="F16">
-        <v>598.0384322545453</v>
+        <v>171.5150624619477</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>103.6196387387974</v>
+        <v>391.0572296167574</v>
       </c>
       <c r="E17">
-        <v>42.30524440800001</v>
+        <v>28.60700094422315</v>
       </c>
       <c r="F17">
-        <v>997.4601008532028</v>
+        <v>353.497957120726</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -10850,7 +10850,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>368.3092047920779</v>
+        <v>387.5648435963337</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -10906,13 +10906,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>14.5285138200122</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>47.51667223700733</v>
+        <v>13.81897056024416</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>1145.965390970871</v>
+        <v>932.0595888896836</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -10989,7 +10989,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1378.273561022978</v>
+        <v>1291.016403574164</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -11045,7 +11045,7 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>1830.911404674807</v>
+        <v>1595.044203983497</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>2186.836600081077</v>
+        <v>1581.586774576236</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2842.749899112663</v>
+        <v>1866.686530957803</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -11213,7 +11213,7 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3951.452696582246</v>
+        <v>2324.284980273127</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>5201.804261509076</v>
+        <v>2844.022102805861</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -11325,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>6512.127689843475</v>
+        <v>3371.693006202082</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -11381,7 +11381,7 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>8603.292300462548</v>
+        <v>4301.374279093905</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -11637,25 +11637,25 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>198.8281728</v>
+        <v>314.7255734013667</v>
       </c>
       <c r="D9">
-        <v>154.8196848</v>
+        <v>95.93209064729841</v>
       </c>
       <c r="E9">
-        <v>492.9549840000001</v>
+        <v>683.0834018366545</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>8.544481942834434</v>
       </c>
       <c r="G9">
-        <v>213.4230336</v>
+        <v>138.4785105235271</v>
       </c>
       <c r="H9">
-        <v>388.6812</v>
+        <v>375.9466678852231</v>
       </c>
       <c r="I9">
-        <v>911.1191904000001</v>
+        <v>899.7891230114308</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -11666,22 +11666,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>245.5014528</v>
+        <v>286.6721121391304</v>
       </c>
       <c r="D10">
-        <v>194.640192</v>
+        <v>158.3342695679337</v>
       </c>
       <c r="E10">
-        <v>608.6700287999998</v>
+        <v>842.6255836634494</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>8.858067885668868</v>
       </c>
       <c r="G10">
-        <v>294.9372864</v>
+        <v>265.3646108049875</v>
       </c>
       <c r="H10">
-        <v>475.5281904000001</v>
+        <v>436.6600432795487</v>
       </c>
       <c r="I10">
         <v>1025.251128</v>
@@ -11695,22 +11695,22 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>316.7097408</v>
+        <v>346.0142855192782</v>
       </c>
       <c r="D11">
-        <v>280.6577856</v>
+        <v>213.7193259798204</v>
       </c>
       <c r="E11">
-        <v>784.2687839999999</v>
+        <v>1052.156918716697</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8.576086917199733</v>
       </c>
       <c r="G11">
-        <v>401.8916304</v>
+        <v>353.8194810733166</v>
       </c>
       <c r="H11">
-        <v>627.1532784000001</v>
+        <v>577.0880731949475</v>
       </c>
       <c r="I11">
         <v>1193.8173552</v>
@@ -11724,22 +11724,22 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>422.8819920000001</v>
+        <v>405.3564588994258</v>
       </c>
       <c r="D12">
-        <v>424.852992</v>
+        <v>269.1199618731169</v>
       </c>
       <c r="E12">
-        <v>1042.3467936</v>
+        <v>1261.688253769946</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>8.294105948730596</v>
       </c>
       <c r="G12">
-        <v>525.500136</v>
+        <v>442.2403433177057</v>
       </c>
       <c r="H12">
-        <v>729.1533168</v>
+        <v>717.5161031103469</v>
       </c>
       <c r="I12">
         <v>1401.3557712</v>
@@ -11753,22 +11753,22 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>514.2701664000001</v>
+        <v>469.7736568597212</v>
       </c>
       <c r="D13">
-        <v>582.4163088</v>
+        <v>328.9451704868005</v>
       </c>
       <c r="E13">
-        <v>1227.7847808</v>
+        <v>1437.047740222729</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>7.219195200869335</v>
       </c>
       <c r="G13">
-        <v>676.4188176000001</v>
+        <v>543.2441744199502</v>
       </c>
       <c r="H13">
-        <v>957.3320448000002</v>
+        <v>945.9831799881753</v>
       </c>
       <c r="I13">
         <v>1707.7437792</v>
@@ -11782,22 +11782,22 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>612.9273888</v>
+        <v>534.1908548200165</v>
       </c>
       <c r="D14">
-        <v>785.9055024</v>
+        <v>388.7703791004841</v>
       </c>
       <c r="E14">
-        <v>1428.2275968</v>
+        <v>1612.407226675512</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6.144284453008077</v>
       </c>
       <c r="G14">
-        <v>847.2682512000001</v>
+        <v>644.2139974982546</v>
       </c>
       <c r="H14">
-        <v>1187.6362992</v>
+        <v>1174.450256866004</v>
       </c>
       <c r="I14">
         <v>2029.8493296</v>
@@ -11811,22 +11811,22 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>723.8395008</v>
+        <v>595.5808451360133</v>
       </c>
       <c r="D15">
-        <v>1016.0867664</v>
+        <v>449.5770950429858</v>
       </c>
       <c r="E15">
-        <v>1656.8162928</v>
+        <v>1781.136354444622</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4.995966933700925</v>
       </c>
       <c r="G15">
-        <v>1049.1617232</v>
+        <v>785.4493209216956</v>
       </c>
       <c r="H15">
-        <v>1407.7134288</v>
+        <v>1468.893378129319</v>
       </c>
       <c r="I15">
         <v>2472.9080544</v>
@@ -11840,22 +11840,22 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>847.3880880000002</v>
+        <v>656.9485765722726</v>
       </c>
       <c r="D16">
-        <v>1286.7854832</v>
+        <v>510.3838109854875</v>
       </c>
       <c r="E16">
-        <v>1911.9898368</v>
+        <v>1949.83548059073</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>3.847649414393771</v>
       </c>
       <c r="G16">
-        <v>1254.0511152</v>
+        <v>926.7526603930172</v>
       </c>
       <c r="H16">
-        <v>1587.5506224</v>
+        <v>1763.336499392636</v>
       </c>
       <c r="I16">
         <v>2962.6684416</v>
@@ -11869,22 +11869,22 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1143.384984</v>
+        <v>773.1621876817067</v>
       </c>
       <c r="D17">
-        <v>1696.5516528</v>
+        <v>630.2523409525917</v>
       </c>
       <c r="E17">
-        <v>2580.095764799999</v>
+        <v>2317.865389969051</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2.013055705244413</v>
       </c>
       <c r="G17">
-        <v>1761.9604704</v>
+        <v>1328.013334862843</v>
       </c>
       <c r="H17">
-        <v>2002.9554288</v>
+        <v>2412.150627297178</v>
       </c>
       <c r="I17">
         <v>4097.5387056</v>
@@ -12191,13 +12191,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.51032</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>91.81029427760741</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -12206,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>14.6752664848608</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>90.12396869280001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -12410,7 +12410,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>138.6762539057669</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>185.9078245805198</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>251.678837933345</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -12761,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>195.1754381600257</v>
+        <v>178.713295137398</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -12776,13 +12776,13 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>368.3092047920779</v>
+        <v>387.5648435963337</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>391.3185753635506</v>
+        <v>368.9488259631841</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -12796,7 +12796,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>690.3776344366688</v>
+        <v>250.654641479095</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -12811,13 +12811,13 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>14.5285138200122</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1123.397453445468</v>
+        <v>1004.009956622219</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -12831,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1279.423735779253</v>
+        <v>335.4324523714831</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -12852,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1476.607199671986</v>
+        <v>1399.503754947649</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -12866,7 +12866,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2067.700294981462</v>
+        <v>448.8842873206123</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -12887,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2234.09231594519</v>
+        <v>1737.312438177103</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>3122.592148728379</v>
+        <v>598.9979507133755</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -12922,7 +12922,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3983.088882952889</v>
+        <v>1702.510781058639</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -12936,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>4019.978864729306</v>
+        <v>636.919316353015</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -12957,7 +12957,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>6799.865344084459</v>
+        <v>1993.955445318681</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>4866.812153090755</v>
+        <v>394.3578017114377</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -12992,7 +12992,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5261.606180819433</v>
+        <v>2462.823946320007</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -13006,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>6091.344939196301</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -13027,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>8858.930237471508</v>
+        <v>3002.788896197674</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -13041,7 +13041,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>7178.173541762352</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>6854.871344397801</v>
+        <v>3551.404855717625</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -13076,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>10369.91479248211</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>18784.97610892163</v>
+        <v>4527.762459768239</v>
       </c>
     </row>
   </sheetData>
@@ -13123,7 +13123,7 @@
         <v>2025</v>
       </c>
       <c r="B2">
-        <v>89.9583586565336</v>
+        <v>80.81465640652657</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -13131,7 +13131,7 @@
         <v>2030</v>
       </c>
       <c r="B3">
-        <v>98.23795078674824</v>
+        <v>90.47230994070755</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -13139,7 +13139,7 @@
         <v>2035</v>
       </c>
       <c r="B4">
-        <v>130.3698695377717</v>
+        <v>102.5109765000132</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -13147,7 +13147,7 @@
         <v>2040</v>
       </c>
       <c r="B5">
-        <v>197.4374247556604</v>
+        <v>109.1456597746855</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -13155,7 +13155,7 @@
         <v>2045</v>
       </c>
       <c r="B6">
-        <v>280.6043104521812</v>
+        <v>118.103570678179</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13163,7 +13163,7 @@
         <v>2050</v>
       </c>
       <c r="B7">
-        <v>276.5800064722745</v>
+        <v>118.291729954893</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -13171,7 +13171,7 @@
         <v>2055</v>
       </c>
       <c r="B8">
-        <v>380.9479131749105</v>
+        <v>131.0670776249844</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -13179,7 +13179,7 @@
         <v>2060</v>
       </c>
       <c r="B9">
-        <v>373.0337549696956</v>
+        <v>142.7116522937507</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -13187,7 +13187,7 @@
         <v>2070</v>
       </c>
       <c r="B10">
-        <v>707.9799012224729</v>
+        <v>144.7904959520824</v>
       </c>
     </row>
   </sheetData>
@@ -13709,7 +13709,7 @@
         <v>74.54584799999999</v>
       </c>
       <c r="C10">
-        <v>81.56021052631577</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -13765,7 +13765,7 @@
         <v>51.941544</v>
       </c>
       <c r="C11">
-        <v>217.8267641379311</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -13821,7 +13821,7 @@
         <v>53.06983199999999</v>
       </c>
       <c r="C12">
-        <v>426.6667982378855</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -13877,7 +13877,7 @@
         <v>43.46031811764706</v>
       </c>
       <c r="C13">
-        <v>219.1141625806452</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>34.21457372093023</v>
       </c>
       <c r="C14">
-        <v>322.8945470270271</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -13989,7 +13989,7 @@
         <v>64.09583620465118</v>
       </c>
       <c r="C15">
-        <v>331.1637976216216</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -14045,7 +14045,7 @@
         <v>65.39445119999999</v>
       </c>
       <c r="C16">
-        <v>154.76292</v>
+        <v>37.65347999999999</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -14060,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>368.3092047920779</v>
+        <v>387.5648435963337</v>
       </c>
       <c r="I16">
         <v>61.91981982053838</v>
@@ -14098,16 +14098,16 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>49.80583991142241</v>
+        <v>14.56580070602383</v>
       </c>
       <c r="C17">
-        <v>138.6161630865805</v>
+        <v>49.05621580481183</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>14.6752664848608</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -14116,10 +14116,10 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>14.5285138200122</v>
       </c>
       <c r="I17">
-        <v>87.62833721268069</v>
+        <v>58.10373527874597</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -14131,7 +14131,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>30.17687196218555</v>
+        <v>16.39499827009207</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -14146,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>861.2501183646723</v>
+        <v>776.7176659374703</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -14154,10 +14154,10 @@
         <v>2030</v>
       </c>
       <c r="B18">
-        <v>82.47925290013198</v>
+        <v>24.08343811615624</v>
       </c>
       <c r="C18">
-        <v>128.2327952268345</v>
+        <v>152.4288956235428</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>119.3955691916528</v>
+        <v>70.41464586517519</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -14187,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>49.07428754699416</v>
+        <v>18.93115190397994</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>973.8786031698305</v>
+        <v>973.8796284209586</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -14210,16 +14210,16 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>145.7026059950382</v>
+        <v>42.5441884182936</v>
       </c>
       <c r="C19">
-        <v>309.6666128908399</v>
+        <v>227.5338122525236</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>90.12396869280001</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>182.1400729355486</v>
+        <v>96.88089329909697</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>84.29766381610573</v>
+        <v>27.9103170792613</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -14266,10 +14266,10 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>238.5844656096046</v>
+        <v>69.66503891149695</v>
       </c>
       <c r="C20">
-        <v>318.3306566441898</v>
+        <v>129.7243384330632</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>262.975734492694</v>
+        <v>132.2432854043108</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -14299,10 +14299,10 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>151.0035577021262</v>
+        <v>43.17345201303107</v>
       </c>
       <c r="N20">
-        <v>6.501179524024765</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -14322,10 +14322,10 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>421.2376629228915</v>
+        <v>122.9984264087105</v>
       </c>
       <c r="C21">
-        <v>447.9394563466996</v>
+        <v>100.8786095379159</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>345.2549525875873</v>
+        <v>181.78957593565</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -14355,10 +14355,10 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>221.144664387979</v>
+        <v>65.99283951446593</v>
       </c>
       <c r="N21">
-        <v>6.537255863488742</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -14378,10 +14378,10 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>711.4250965235001</v>
+        <v>207.7305284488233</v>
       </c>
       <c r="C22">
-        <v>752.4739872034063</v>
+        <v>65.40296161665326</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -14399,7 +14399,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>450.9381518941906</v>
+        <v>240.3036596903256</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -14411,10 +14411,10 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>312.8429296064319</v>
+        <v>102.983128547124</v>
       </c>
       <c r="N22">
-        <v>6.57258836090192</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -14434,16 +14434,16 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>1162.696651661739</v>
+        <v>342.9146993962111</v>
       </c>
       <c r="C23">
-        <v>843.8974133282264</v>
+        <v>52.38237763353817</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>138.6762539057669</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -14455,7 +14455,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>577.2959310945529</v>
+        <v>292.1831127545508</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -14467,10 +14467,10 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>443.3508939936337</v>
+        <v>141.5067886059715</v>
       </c>
       <c r="N23">
-        <v>6.642509513677472</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -14490,16 +14490,16 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>1584.316759287081</v>
+        <v>565.29603974114</v>
       </c>
       <c r="C24">
-        <v>939.7607718948527</v>
+        <v>41.63831173228932</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>185.9078245805198</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -14511,7 +14511,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>735.6144620390003</v>
+        <v>321.0572048570864</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -14523,10 +14523,10 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>629.3917915105454</v>
+        <v>195.8221597951218</v>
       </c>
       <c r="N24">
-        <v>6.712430666453024</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -14538,7 +14538,7 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>2376.626183238008</v>
+        <v>2214.578743131747</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -14546,16 +14546,16 @@
         <v>2070</v>
       </c>
       <c r="B25">
-        <v>2235.356807218757</v>
+        <v>1087.418342006971</v>
       </c>
       <c r="C25">
-        <v>1229.086976453342</v>
+        <v>61.15694662058688</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>251.678837933345</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -14567,7 +14567,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1084.695300990844</v>
+        <v>377.369064377907</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -14579,10 +14579,10 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1039.765345261203</v>
+        <v>382.1049580649492</v>
       </c>
       <c r="N25">
-        <v>6.642509513677472</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -14594,7 +14594,7 @@
         <v>0</v>
       </c>
       <c r="R25">
-        <v>2684.907683325759</v>
+        <v>2350.922794698759</v>
       </c>
     </row>
   </sheetData>
@@ -15520,7 +15520,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>136.4927356872388</v>
+        <v>232.5270254215627</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -15541,10 +15541,10 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>2359.277023936049</v>
+        <v>3207.71687891157</v>
       </c>
       <c r="O17">
-        <v>1558.442070593878</v>
+        <v>1826.736854506157</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -15597,10 +15597,10 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1830.837151193212</v>
+        <v>3062.49413236974</v>
       </c>
       <c r="O18">
-        <v>1063.211879323572</v>
+        <v>1714.723091789007</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -15653,10 +15653,10 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>1353.919744782195</v>
+        <v>3945.785705607872</v>
       </c>
       <c r="O19">
-        <v>688.6675776645933</v>
+        <v>2201.898386415952</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -15709,10 +15709,10 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>1345.532664257901</v>
+        <v>4126.101390141332</v>
       </c>
       <c r="O20">
-        <v>684.749447459492</v>
+        <v>2244.620794459548</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -15765,10 +15765,10 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>1249.613064263628</v>
+        <v>4237.530848850293</v>
       </c>
       <c r="O21">
-        <v>636.0973423981239</v>
+        <v>2291.073629075113</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -15821,10 +15821,10 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1249.942819236359</v>
+        <v>3961.692471347238</v>
       </c>
       <c r="O22">
-        <v>636.4270973708549</v>
+        <v>2046.583797192817</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -15877,10 +15877,10 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>973.4760101583677</v>
+        <v>4128.259662241494</v>
       </c>
       <c r="O23">
-        <v>495.9126465230621</v>
+        <v>2105.837129389162</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -15933,10 +15933,10 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>693.2176447118803</v>
+        <v>4130.981771982262</v>
       </c>
       <c r="O24">
-        <v>366.833688933229</v>
+        <v>2108.558906623331</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -15989,10 +15989,10 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>211.3323609204995</v>
+        <v>3577.477068235014</v>
       </c>
       <c r="O25">
-        <v>107.7127221817021</v>
+        <v>1826.446110795794</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -16859,7 +16859,7 @@
         <v>316.519710967742</v>
       </c>
       <c r="C16">
-        <v>370.811533655388</v>
+        <v>384.015971360883</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -16912,10 +16912,10 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>358.9180143515692</v>
+        <v>473.7092053906528</v>
       </c>
       <c r="C17">
-        <v>376.3291757181413</v>
+        <v>321.7256869005805</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -16933,19 +16933,19 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>249.1595458293232</v>
+        <v>512.612105993562</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>245.587867187203</v>
+        <v>52.64287919214283</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>160.5916703987895</v>
+        <v>290.2709446922496</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -16960,7 +16960,7 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>32.16572276248839</v>
+        <v>104.387768328948</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -16968,10 +16968,10 @@
         <v>2030</v>
       </c>
       <c r="B18">
-        <v>359.8635740062311</v>
+        <v>496.399481215471</v>
       </c>
       <c r="C18">
-        <v>268.7037141571588</v>
+        <v>278.1254169456554</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -16989,19 +16989,19 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>211.333507359275</v>
+        <v>583.6305991301112</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>42.14631312756684</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>196.4271652530058</v>
+        <v>267.7409602351505</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -17016,7 +17016,7 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>0.001025251128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -17024,10 +17024,10 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>284.1371868232393</v>
+        <v>656.3846420760549</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>353.8591799052284</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -17045,19 +17045,19 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>148.7029033104683</v>
+        <v>769.3987086758484</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>42.14631312756684</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>232.4120769838943</v>
+        <v>318.1039684400169</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -17080,10 +17080,10 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>243.2784909826977</v>
+        <v>750.1642606168867</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>252.404004408818</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -17101,19 +17101,19 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>145.6262915178378</v>
+        <v>769.1333281785029</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>42.14631312756684</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>271.8784342978738</v>
+        <v>362.1830068863948</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -17136,10 +17136,10 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>241.4538776453556</v>
+        <v>788.5261910341208</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>233.5877495472325</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -17157,19 +17157,19 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>78.9363422081274</v>
+        <v>754.1502113958049</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>39.38874545532467</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>293.1255020120211</v>
+        <v>403.7808173452552</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -17192,10 +17192,10 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>296.9422617580922</v>
+        <v>791.0071367405073</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>54.78961712914365</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -17213,19 +17213,19 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>16.48900091384368</v>
+        <v>692.8938111410209</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>5.170456881147216</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>300.0844591935681</v>
+        <v>431.2077262728925</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -17248,7 +17248,7 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>197.0747568289391</v>
+        <v>816.3172139459172</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -17269,19 +17269,19 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>752.0312623763732</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>5.711514925107435</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>280.4886068063663</v>
+        <v>454.0740565300418</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -17304,10 +17304,10 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>108.3876592891965</v>
+        <v>660.3701149883145</v>
       </c>
       <c r="C24">
-        <v>27.55722762485962</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -17325,19 +17325,19 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>900.9263335934656</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>6.252476360248183</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>217.9962964894547</v>
+        <v>461.1264167771508</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -17360,7 +17360,7 @@
         <v>2070</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>337.3802475937196</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -17381,19 +17381,19 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1022.593480228744</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>6.252476360248183</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>103.6196387387974</v>
+        <v>391.0572296167574</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -18281,7 +18281,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>195.1754381600257</v>
+        <v>178.713295137398</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -18337,7 +18337,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>690.3776344366688</v>
+        <v>250.654641479095</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -18393,7 +18393,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1279.423735779253</v>
+        <v>335.4324523714831</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -18414,7 +18414,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>38.38378213174446</v>
+        <v>227.1572063745956</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -18449,7 +18449,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>2067.700294981462</v>
+        <v>448.8842873206123</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -18470,7 +18470,7 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>40.19988687461316</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -18505,7 +18505,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>3122.592148728379</v>
+        <v>598.9979507133755</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -18561,7 +18561,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>4019.978864729306</v>
+        <v>636.919316353015</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -18617,7 +18617,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>4866.812153090755</v>
+        <v>394.3578017114377</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -18673,7 +18673,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>6091.344939196301</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -18729,7 +18729,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>7178.173541762352</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -18785,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>10369.91479248211</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -19673,7 +19673,7 @@
         <v>0.03504000000000001</v>
       </c>
       <c r="C16">
-        <v>231.8240405488011</v>
+        <v>218.5035166490604</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -19729,7 +19729,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>556.0621650301341</v>
+        <v>192.9248577015675</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -19750,7 +19750,7 @@
         <v>260.3229418542278</v>
       </c>
       <c r="J17">
-        <v>107.9924369022894</v>
+        <v>31.40675127328218</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -19785,7 +19785,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>952.1876695082209</v>
+        <v>281.7441809533407</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -19803,7 +19803,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>365.6198484027769</v>
+        <v>280.8454777927381</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -19841,7 +19841,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1528.985763992018</v>
+        <v>242.2067917156955</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -19859,7 +19859,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>538.7145309894438</v>
+        <v>246.87738247953</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -19897,7 +19897,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>2308.344013045345</v>
+        <v>225.8514382978724</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>814.2481356830333</v>
+        <v>373.1465124155031</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>2896.682803860692</v>
+        <v>225.8514382978724</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -19971,7 +19971,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>1123.296060868614</v>
+        <v>411.0678780551426</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -20009,7 +20009,7 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>3464.58347429035</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -20027,7 +20027,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>1402.228678800404</v>
+        <v>394.3578017114376</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -20065,7 +20065,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>4364.015065141929</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -20083,7 +20083,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>1727.329874054372</v>
+        <v>355.6035477932625</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -20121,7 +20121,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>5188.434964411343</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -20139,7 +20139,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>1989.73857735101</v>
+        <v>317.0231629672436</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -20177,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>6964.030169443414</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -20195,7 +20195,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>2384.504166209496</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -21169,7 +21169,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>2077.378957076557</v>
+        <v>996.468043236223</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -21225,7 +21225,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>2301.560828754586</v>
+        <v>1155.017660059078</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -21281,7 +21281,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>2649.050605449998</v>
+        <v>1156.570176179968</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -21337,7 +21337,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>2653.27184909377</v>
+        <v>1188.717787804626</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -21393,7 +21393,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>2540.939768444955</v>
+        <v>1224.510453614532</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -21449,7 +21449,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>2180.921851051019</v>
+        <v>1254.955677558266</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -21505,7 +21505,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1885.230682751674</v>
+        <v>1264.524990219159</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -21561,7 +21561,7 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1665.027630486207</v>
+        <v>1274.094302880052</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -21617,7 +21617,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>1576.8</v>
+        <v>1287.773293135434</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -22487,7 +22487,7 @@
         <v>172.951308</v>
       </c>
       <c r="C16">
-        <v>8.535744000000001</v>
+        <v>6.773520000067201</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -22540,13 +22540,13 @@
         <v>2025</v>
       </c>
       <c r="B17">
-        <v>257.6413837374894</v>
+        <v>100.4514458971557</v>
       </c>
       <c r="C17">
-        <v>232.2105697380825</v>
+        <v>8.451647999999999</v>
       </c>
       <c r="D17">
-        <v>286.4767460220231</v>
+        <v>71.78574435292204</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -22555,7 +22555,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>315.0498004363636</v>
+        <v>158.248596220568</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -22570,7 +22570,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>71.20401619028696</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -22596,13 +22596,13 @@
         <v>2030</v>
       </c>
       <c r="B18">
-        <v>375.9812981574944</v>
+        <v>131.3498557603812</v>
       </c>
       <c r="C18">
-        <v>253.077695580543</v>
+        <v>9.248973283018868</v>
       </c>
       <c r="D18">
-        <v>72.25947974678616</v>
+        <v>68.07418227732943</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -22617,7 +22617,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>348.7795305970911</v>
+        <v>370.5887802986966</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -22626,7 +22626,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>73.8172323805739</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -22652,13 +22652,13 @@
         <v>2035</v>
       </c>
       <c r="B19">
-        <v>585.4313094873154</v>
+        <v>59.20352824781965</v>
       </c>
       <c r="C19">
-        <v>374.0383143631607</v>
+        <v>10.04629856603773</v>
       </c>
       <c r="D19">
-        <v>72.25947974678616</v>
+        <v>68.07418227732943</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -22673,7 +22673,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>486.8192959626826</v>
+        <v>444.2876239321487</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -22682,7 +22682,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>71.46739097666443</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -22708,13 +22708,13 @@
         <v>2040</v>
       </c>
       <c r="B20">
-        <v>613.7603271154347</v>
+        <v>2.307383917110581</v>
       </c>
       <c r="C20">
-        <v>428.0686711594438</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>72.25947974678616</v>
+        <v>48.32271062261941</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -22729,7 +22729,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>462.7115219783352</v>
+        <v>533.3313798875151</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -22738,7 +22738,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>69.11754957275497</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -22764,13 +22764,13 @@
         <v>2045</v>
       </c>
       <c r="B21">
-        <v>594.3871577963237</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>540.4007518082586</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>72.25947974678616</v>
+        <v>21.48763437822335</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -22785,7 +22785,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>369.7526106486316</v>
+        <v>571.4314296145321</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -22794,7 +22794,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>60.15996000724446</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -22820,10 +22820,10 @@
         <v>2050</v>
       </c>
       <c r="B22">
-        <v>390.0046948428908</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>653.4686375627789</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -22841,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>214.1171562081283</v>
+        <v>601.8766535582661</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -22850,7 +22850,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>51.20237044173398</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -22876,10 +22876,10 @@
         <v>2055</v>
       </c>
       <c r="B23">
-        <v>220.090349826137</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>794.2313887739838</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -22897,7 +22897,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>88.34033292553653</v>
+        <v>611.445966219159</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -22906,7 +22906,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>41.63305778084104</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -22932,10 +22932,10 @@
         <v>2060</v>
       </c>
       <c r="B24">
-        <v>88.22763048620732</v>
+        <v>54.3414476570625</v>
       </c>
       <c r="C24">
-        <v>976.6355075354801</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -22953,7 +22953,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>566.6738312229893</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -22962,7 +22962,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>32.06374511994809</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -22991,10 +22991,10 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>1427.84458809087</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1.609290654195669</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -23009,7 +23009,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>634.6942691354342</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>16.77546421037011</v>
       </c>
       <c r="M25">
         <v>0</v>
